--- a/test-uploads-v2/06_project-schedule/project-schedule.xlsx
+++ b/test-uploads-v2/06_project-schedule/project-schedule.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +27,13 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -40,16 +42,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EBF3FB"/>
+        <fgColor rgb="001A2E44"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -57,35 +54,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,681 +426,432 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Task ID</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Task Name</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Predecessor</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>End Date</t>
+          <t>Milestone Type</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Duration (Days)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Assigned To</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Milestone Label</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>T-001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CIVIL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Site Preparation &amp; Marking</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>01-Aug-2026</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>07-Aug-2026</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>T-002</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CIVIL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Foundation Excavation</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>T-001</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>08-Aug-2026</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>18-Aug-2026</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>T-003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CIVIL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>PCC &amp; RCC Foundation</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>T-002</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>19-Aug-2026</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>28-Aug-2026</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7 days curing</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>T-004</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CIVIL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Plinth Beam</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>T-003</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>29-Aug-2026</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>05-Sep-2026</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>T-005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CIVIL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Ground Floor Columns</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>T-004</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>06-Sep-2026</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>15-Sep-2026</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>T-006</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CIVIL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Ground Floor Slab</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>T-005</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>16-Sep-2026</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>26-Sep-2026</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ground Floor Slab Complete</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>T-007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CIVIL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Ground Floor Brickwork</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>T-006</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>27-Sep-2026</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>10-Oct-2026</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>T-008</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CIVIL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>First Floor Columns</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>T-006</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>27-Sep-2026</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>06-Oct-2026</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>T-009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CIVIL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>First Floor Slab</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>T-008</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>07-Oct-2026</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>17-Oct-2026</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>First Floor Slab Complete</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>T-010</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FINISHING</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Plastering (Internal)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>T-007</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>11-Oct-2026</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>01-Nov-2026</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>T-011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MEP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Electrical Rough-in</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>T-007</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>11-Oct-2026</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>25-Oct-2026</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>T-012</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MEP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Plumbing Rough-in</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>T-007</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>11-Oct-2026</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>25-Oct-2026</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>T-013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FINISHING</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Flooring</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>T-010</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>02-Nov-2026</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>20-Nov-2026</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>T-014</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FINISHING</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Painting</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>T-013</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>21-Nov-2026</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>05-Dec-2026</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Site Manager</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>T-015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HANDOVER</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Handover</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>T-014</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>06-Dec-2026</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>10-Dec-2026</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>PMC Head</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Handover Complete</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
